--- a/Employee_Reports_wi48/Ifras Mohammed Q0598.xlsx
+++ b/Employee_Reports_wi48/Ifras Mohammed Q0598.xlsx
@@ -560,11 +560,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -609,11 +609,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -658,11 +658,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -695,11 +695,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
